--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_125_R13.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_125_R13.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. LO</t>
+          <t>S. FRANCISCO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.5401</v>
+        <v>6.0461</v>
       </c>
       <c r="E2" t="n">
-        <v>1.9759</v>
+        <v>2.9903</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5642</v>
+        <v>3.0557</v>
       </c>
       <c r="G2" t="n">
-        <v>1.5204</v>
+        <v>7.0387</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.1368</v>
+        <v>2.2541</v>
       </c>
       <c r="I2" t="n">
-        <v>3.6571</v>
+        <v>4.7846</v>
       </c>
       <c r="J2" t="n">
-        <v>1.1169</v>
+        <v>7.8037</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.7036</v>
+        <v>2.3835</v>
       </c>
       <c r="L2" t="n">
-        <v>2.8205</v>
+        <v>5.4203</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4035</v>
+        <v>-0.765</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4331</v>
+        <v>-0.1294</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8366</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.4639</v>
+        <v>-4.871</v>
       </c>
       <c r="R2" t="n">
-        <v>1.8556</v>
+        <v>3.7112</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4837</v>
+        <v>-0.6526</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.8215</v>
+        <v>-0.9039</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3052</v>
+        <v>0.2513</v>
       </c>
       <c r="V2" t="n">
-        <v>2.1444</v>
+        <v>0.8197</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1444</v>
+        <v>0.9615</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. FRANCISCO</t>
+          <t>M. LO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.4563</v>
+        <v>5.3227</v>
       </c>
       <c r="E3" t="n">
-        <v>2.4006</v>
+        <v>2.3298</v>
       </c>
       <c r="F3" t="n">
-        <v>3.0557</v>
+        <v>2.9929</v>
       </c>
       <c r="G3" t="n">
-        <v>7.0387</v>
+        <v>1.5204</v>
       </c>
       <c r="H3" t="n">
-        <v>2.2541</v>
+        <v>-2.1368</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7846</v>
+        <v>3.6571</v>
       </c>
       <c r="J3" t="n">
-        <v>7.8037</v>
+        <v>1.1169</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3835</v>
+        <v>-1.7036</v>
       </c>
       <c r="L3" t="n">
-        <v>5.4203</v>
+        <v>2.8205</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.765</v>
+        <v>0.4035</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.1294</v>
+        <v>-0.4331</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6356000000000001</v>
+        <v>0.8366</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.871</v>
+        <v>-0.4639</v>
       </c>
       <c r="R3" t="n">
-        <v>3.7112</v>
+        <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.2423</v>
+        <v>0.2662</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.4936</v>
+        <v>-0.4676</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2513</v>
+        <v>0.7339</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8197</v>
+        <v>2.1444</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9615</v>
+        <v>2.1444</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. TUBELIS</t>
+          <t>I. BRAZDEIKIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.2104</v>
+        <v>3.6784</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0794</v>
+        <v>1.6887</v>
       </c>
       <c r="F4" t="n">
-        <v>4.2898</v>
+        <v>1.9896</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4933</v>
+        <v>3.2783</v>
       </c>
       <c r="H4" t="n">
-        <v>-4.9701</v>
+        <v>-0.4525</v>
       </c>
       <c r="I4" t="n">
-        <v>4.4769</v>
+        <v>3.7307</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.8296</v>
+        <v>2.7499</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.3126</v>
+        <v>-0.1443</v>
       </c>
       <c r="L4" t="n">
-        <v>3.483</v>
+        <v>2.8942</v>
       </c>
       <c r="M4" t="n">
-        <v>1.3363</v>
+        <v>0.5284</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3424</v>
+        <v>-0.3082</v>
       </c>
       <c r="O4" t="n">
-        <v>0.9939</v>
+        <v>0.8366</v>
       </c>
       <c r="P4" t="n">
-        <v>1.6237</v>
+        <v>2.5515</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.6237</v>
+        <v>-0.232</v>
       </c>
       <c r="R4" t="n">
-        <v>3.2473</v>
+        <v>2.7834</v>
       </c>
       <c r="S4" t="n">
-        <v>3.2218</v>
+        <v>-1.0791</v>
       </c>
       <c r="T4" t="n">
-        <v>3.3738</v>
+        <v>-0.8292</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.152</v>
+        <v>-0.25</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>I. BRAZDEIKIS</t>
+          <t>A. TUBELIS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0214</v>
+        <v>2.0188</v>
       </c>
       <c r="E5" t="n">
-        <v>1.099</v>
+        <v>-2.6743</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9224</v>
+        <v>4.6931</v>
       </c>
       <c r="G5" t="n">
-        <v>3.2783</v>
+        <v>-0.4933</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4525</v>
+        <v>-4.9701</v>
       </c>
       <c r="I5" t="n">
-        <v>3.7307</v>
+        <v>4.4769</v>
       </c>
       <c r="J5" t="n">
-        <v>2.7499</v>
+        <v>-1.8296</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1443</v>
+        <v>-5.3126</v>
       </c>
       <c r="L5" t="n">
-        <v>2.8942</v>
+        <v>3.483</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5284</v>
+        <v>1.3363</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3082</v>
+        <v>0.3424</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8366</v>
+        <v>0.9939</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5515</v>
+        <v>1.6237</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.232</v>
+        <v>-1.6237</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7834</v>
+        <v>3.2473</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.7361</v>
+        <v>1.0302</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.4189</v>
+        <v>0.7789</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3172</v>
+        <v>0.2513</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1434</v>
+        <v>1.6551</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3592</v>
+        <v>1.0053</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7842</v>
+        <v>0.6498</v>
       </c>
       <c r="G6" t="n">
         <v>1.9264</v>
@@ -922,13 +922,13 @@
         <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6808999999999999</v>
+        <v>0.1926</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3383</v>
+        <v>-0.0156</v>
       </c>
       <c r="U6" t="n">
-        <v>0.3427</v>
+        <v>0.2082</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. BIRUTIS</t>
+          <t>E. ULANOVAS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1296</v>
+        <v>0.0959</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.1536</v>
+        <v>-1.9831</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0241</v>
+        <v>2.079</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.698</v>
+        <v>-0.4687</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4705</v>
+        <v>-1.5797</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.2275</v>
+        <v>1.1109</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0704</v>
+        <v>0.1929</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0336</v>
+        <v>-1.0819</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0368</v>
+        <v>1.2747</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7684</v>
+        <v>-0.6616</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5041</v>
+        <v>-0.4978</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2643</v>
+        <v>-0.1638</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4639</v>
+        <v>3.0154</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-0.4639</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4639</v>
+        <v>3.4793</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1046</v>
+        <v>-0.4481</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.224</v>
+        <v>-0.9234</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3286</v>
+        <v>0.4753</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-2.0026</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.7886</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. SIRVYDIS</t>
+          <t>L. BIRUTIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2356</v>
+        <v>-0.0788</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.8406</v>
+        <v>-0.0357</v>
       </c>
       <c r="F8" t="n">
-        <v>0.605</v>
+        <v>-0.0432</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3524</v>
+        <v>-0.698</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6364</v>
+        <v>-0.4705</v>
       </c>
       <c r="I8" t="n">
-        <v>0.716</v>
+        <v>-0.2275</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8207</v>
+        <v>0.0704</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8907</v>
+        <v>0.0336</v>
       </c>
       <c r="L8" t="n">
-        <v>0.93</v>
+        <v>0.0368</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4683</v>
+        <v>-0.7684</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2543</v>
+        <v>-0.5041</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.214</v>
+        <v>-0.2643</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6237</v>
+        <v>0.4639</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4121</v>
+        <v>0.1553</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1098</v>
+        <v>-0.1061</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5219</v>
+        <v>0.2614</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4263</v>
+        <v>-0.2912</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.07580000000000001</v>
+        <v>0.1602</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3505</v>
+        <v>-0.4513</v>
       </c>
       <c r="G9" t="n">
         <v>-0.8201000000000001</v>
@@ -1156,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0004</v>
+        <v>0.1346</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1494</v>
+        <v>0.08649999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1489</v>
+        <v>0.0481</v>
       </c>
       <c r="V9" t="n">
         <v>0.3943</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. ULANOVAS</t>
+          <t>D. SIRVYDIS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3854</v>
+        <v>-0.337</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9267</v>
+        <v>-1.0765</v>
       </c>
       <c r="F10" t="n">
-        <v>1.5413</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4687</v>
+        <v>1.3524</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.5797</v>
+        <v>0.6364</v>
       </c>
       <c r="I10" t="n">
-        <v>1.1109</v>
+        <v>0.716</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1929</v>
+        <v>1.8207</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.0819</v>
+        <v>0.8907</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2747</v>
+        <v>0.93</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6616</v>
+        <v>-0.4683</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.4978</v>
+        <v>-0.2543</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1638</v>
+        <v>-0.214</v>
       </c>
       <c r="P10" t="n">
-        <v>3.0154</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.4639</v>
+        <v>-2.5515</v>
       </c>
       <c r="R10" t="n">
-        <v>3.4793</v>
+        <v>1.6237</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.9294</v>
+        <v>0.3106</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.867</v>
+        <v>-0.3457</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0624</v>
+        <v>0.6563</v>
       </c>
       <c r="V10" t="n">
-        <v>-2.0026</v>
+        <v>-1.0722</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.7886</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.2873</v>
+        <v>-4.2023</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.147</v>
+        <v>-3.7932</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.1403</v>
+        <v>-0.4091</v>
       </c>
       <c r="G11" t="n">
         <v>-2.0613</v>
@@ -1312,13 +1312,13 @@
         <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7415</v>
+        <v>-0.6565</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0455</v>
+        <v>-0.6917</v>
       </c>
       <c r="U11" t="n">
-        <v>0.304</v>
+        <v>0.0351</v>
       </c>
       <c r="V11" t="n">
         <v>-0.7886</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>13.9074</v>
+        <v>13.9077</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.388399999999999</v>
+        <v>-1.3885</v>
       </c>
       <c r="F12" t="n">
         <v>15.2959</v>
@@ -1390,13 +1390,13 @@
         <v>18.5561</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.7465999999999999</v>
+        <v>-0.7467999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.4176</v>
+        <v>-3.4178</v>
       </c>
       <c r="U12" t="n">
-        <v>2.671</v>
+        <v>2.6709</v>
       </c>
       <c r="V12" t="n">
         <v>-1.719</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K. DIOP</t>
+          <t>R. VILLAR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.1501</v>
+        <v>2.0196</v>
       </c>
       <c r="E13" t="n">
-        <v>0.5203</v>
+        <v>-0.2188</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6298</v>
+        <v>2.2384</v>
       </c>
       <c r="G13" t="n">
-        <v>0.49</v>
+        <v>-0.1529</v>
       </c>
       <c r="H13" t="n">
-        <v>1.8752</v>
+        <v>1.4766</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.3851</v>
+        <v>-1.6295</v>
       </c>
       <c r="J13" t="n">
-        <v>1.0115</v>
+        <v>-0.3998</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9747</v>
+        <v>0.3865</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0368</v>
+        <v>-0.7863</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.5215</v>
+        <v>0.247</v>
       </c>
       <c r="N13" t="n">
-        <v>0.9005</v>
+        <v>1.0901</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.422</v>
+        <v>-0.8431</v>
       </c>
       <c r="P13" t="n">
+        <v>0.6959</v>
+      </c>
+      <c r="Q13" t="n">
         <v>-0.232</v>
       </c>
-      <c r="Q13" t="n">
-        <v>-1.3917</v>
-      </c>
       <c r="R13" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>1.8921</v>
+        <v>0.6879</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9006</v>
+        <v>0.4129</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9915</v>
+        <v>0.275</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R. VILLAR</t>
+          <t>K. DIOP</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0196</v>
+        <v>1.1907</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2188</v>
+        <v>-0.0694</v>
       </c>
       <c r="F14" t="n">
-        <v>2.2384</v>
+        <v>1.2601</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.1529</v>
+        <v>0.49</v>
       </c>
       <c r="H14" t="n">
-        <v>1.4766</v>
+        <v>1.8752</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.6295</v>
+        <v>-1.3851</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3998</v>
+        <v>1.0115</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3865</v>
+        <v>0.9747</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.7863</v>
+        <v>0.0368</v>
       </c>
       <c r="M14" t="n">
-        <v>0.247</v>
+        <v>-0.5215</v>
       </c>
       <c r="N14" t="n">
-        <v>1.0901</v>
+        <v>0.9005</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8431</v>
+        <v>-1.422</v>
       </c>
       <c r="P14" t="n">
-        <v>0.6959</v>
+        <v>-0.232</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6879</v>
+        <v>0.9326</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4129</v>
+        <v>0.3108</v>
       </c>
       <c r="U14" t="n">
-        <v>0.275</v>
+        <v>0.6218</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R. KURUCS</t>
+          <t>M. DIAKITE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6445</v>
+        <v>0.114</v>
       </c>
       <c r="E15" t="n">
-        <v>1.3403</v>
+        <v>-0.2084</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.6958</v>
+        <v>0.3224</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2033</v>
+        <v>-2.254</v>
       </c>
       <c r="H15" t="n">
-        <v>3.3084</v>
+        <v>-0.7718</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.1051</v>
+        <v>-1.4822</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4932</v>
+        <v>-0.5027</v>
       </c>
       <c r="K15" t="n">
-        <v>2.4402</v>
+        <v>-0.9677</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.947</v>
+        <v>0.465</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.2899</v>
+        <v>-1.7513</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8681</v>
+        <v>0.196</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.1581</v>
+        <v>-1.9473</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>0.9278</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S15" t="n">
-        <v>1.5134</v>
+        <v>-0.4206</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2388</v>
+        <v>-0.6877</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2746</v>
+        <v>0.2671</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.0722</v>
+        <v>1.8608</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.214</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.0722</v>
+        <v>0.6468</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. DIAKITE</t>
+          <t>R. KURUCS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6022999999999999</v>
+        <v>-0.0639</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1455</v>
+        <v>0.3967</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4568</v>
+        <v>-0.4606</v>
       </c>
       <c r="G16" t="n">
-        <v>-2.254</v>
+        <v>0.2033</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.7718</v>
+        <v>3.3084</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.4822</v>
+        <v>-3.1051</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.5027</v>
+        <v>1.4932</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.9677</v>
+        <v>2.4402</v>
       </c>
       <c r="L16" t="n">
-        <v>0.465</v>
+        <v>-0.947</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7513</v>
+        <v>-1.2899</v>
       </c>
       <c r="N16" t="n">
-        <v>0.196</v>
+        <v>0.8681</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.9473</v>
+        <v>-2.1581</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0677</v>
+        <v>0.805</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.3339</v>
+        <v>0.2952</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4015</v>
+        <v>0.5098</v>
       </c>
       <c r="V16" t="n">
-        <v>1.8608</v>
+        <v>-1.0722</v>
       </c>
       <c r="W16" t="n">
-        <v>1.214</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0.6468</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. SEDEKERSKIS</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.6807</v>
+        <v>-0.4998</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6852</v>
+        <v>-0.2019</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0045</v>
+        <v>-0.2979</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.1481</v>
+        <v>-2.7445</v>
       </c>
       <c r="H17" t="n">
-        <v>0.4106</v>
+        <v>2.067</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.5587</v>
+        <v>-4.8115</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8633999999999999</v>
+        <v>-0.897</v>
       </c>
       <c r="K17" t="n">
-        <v>0.7897999999999999</v>
+        <v>1.3885</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0736</v>
+        <v>-2.2854</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0116</v>
+        <v>-1.8476</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3792</v>
+        <v>0.6785</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6323</v>
+        <v>-2.5261</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6959</v>
+        <v>0.6959</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0215</v>
+        <v>0.4766</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2987</v>
+        <v>-0.1452</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3203</v>
+        <v>0.6218</v>
       </c>
       <c r="V17" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="W17" t="n">
-        <v>0.1418</v>
+        <v>1.0722</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>T. SEDEKERSKIS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.722</v>
+        <v>-0.7307</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0095</v>
+        <v>-0.5672</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2874</v>
+        <v>-0.1635</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0198</v>
+        <v>-0.1481</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.4418</v>
+        <v>0.4106</v>
       </c>
       <c r="I18" t="n">
-        <v>1.422</v>
+        <v>-0.5587</v>
       </c>
       <c r="J18" t="n">
-        <v>1.1103</v>
+        <v>0.8633999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.4697</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>3.58</v>
+        <v>0.0736</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.1302</v>
+        <v>-1.0116</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0279</v>
+        <v>-0.3792</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.1581</v>
+        <v>-0.6323</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.1598</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.7834</v>
+        <v>-1.3917</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4033</v>
+        <v>-0.0286</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4086</v>
+        <v>-0.1808</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0053</v>
+        <v>0.1522</v>
       </c>
       <c r="V18" t="n">
-        <v>1.8608</v>
+        <v>0.1418</v>
       </c>
       <c r="W18" t="n">
-        <v>1.0722</v>
+        <v>0.1418</v>
       </c>
       <c r="X18" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. FRISCH</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2229</v>
+        <v>-0.8907</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9873</v>
+        <v>-1.2454</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2356</v>
+        <v>0.3546</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1831</v>
+        <v>-1.0198</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7036</v>
+        <v>-2.4418</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.8867</v>
+        <v>1.422</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5459000000000001</v>
+        <v>1.1103</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1176</v>
+        <v>-2.4697</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4282</v>
+        <v>3.58</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.729</v>
+        <v>-2.1302</v>
       </c>
       <c r="N19" t="n">
-        <v>0.586</v>
+        <v>0.0279</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3149</v>
+        <v>-2.1581</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.4639</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.1598</v>
+        <v>-2.7834</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5759</v>
+        <v>-0.572</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3734</v>
+        <v>-0.6445</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2025</v>
+        <v>0.0725</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.8608</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>C. FRISCH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6279</v>
+        <v>-0.9370000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0276</v>
+        <v>-0.8694</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6004</v>
+        <v>-0.06759999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.7445</v>
+        <v>-0.1831</v>
       </c>
       <c r="H20" t="n">
-        <v>2.067</v>
+        <v>0.7036</v>
       </c>
       <c r="I20" t="n">
-        <v>-4.8115</v>
+        <v>-0.8867</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.897</v>
+        <v>0.5459000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3885</v>
+        <v>0.1176</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.2854</v>
+        <v>0.4282</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.8476</v>
+        <v>-0.729</v>
       </c>
       <c r="N20" t="n">
-        <v>0.6785</v>
+        <v>0.586</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.5261</v>
+        <v>-1.3149</v>
       </c>
       <c r="P20" t="n">
+        <v>-0.4639</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-1.1598</v>
+      </c>
+      <c r="R20" t="n">
         <v>0.6959</v>
       </c>
-      <c r="Q20" t="n">
-        <v>-0.232</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0.9278</v>
-      </c>
       <c r="S20" t="n">
-        <v>-0.6515</v>
+        <v>-0.2899</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.9709</v>
+        <v>-0.2555</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3194</v>
+        <v>-0.0345</v>
       </c>
       <c r="V20" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6804</v>
+        <v>-2.5289</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0929</v>
+        <v>-1.9749</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.5875</v>
+        <v>-0.5538999999999999</v>
       </c>
       <c r="G21" t="n">
         <v>1.0059</v>
@@ -2092,13 +2092,13 @@
         <v>1.3917</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0627</v>
+        <v>-0.9111</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.0455</v>
+        <v>-0.9276</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.0171</v>
+        <v>0.0165</v>
       </c>
       <c r="V21" t="n">
         <v>-0.5361</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9494</v>
+        <v>-4.4275</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.4274</v>
+        <v>-3.0736</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.522</v>
+        <v>-1.3539</v>
       </c>
       <c r="G22" t="n">
         <v>-1.2165</v>
@@ -2170,13 +2170,13 @@
         <v>1.6237</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3385</v>
+        <v>-0.8167</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1949</v>
+        <v>-0.841</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1436</v>
+        <v>0.0244</v>
       </c>
       <c r="V22" t="n">
         <v>-1.4665</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.4407</v>
+        <v>-7.1534</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.8534</v>
+        <v>-7.2637</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4128</v>
+        <v>0.1103</v>
       </c>
       <c r="G23" t="n">
         <v>-4.5549</v>
@@ -2248,13 +2248,13 @@
         <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5961</v>
+        <v>0.8834</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5975</v>
+        <v>-0.0077</v>
       </c>
       <c r="U23" t="n">
-        <v>1.1936</v>
+        <v>0.8911</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9304</v>
@@ -2281,7 +2281,7 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-13.9075</v>
+        <v>-13.9076</v>
       </c>
       <c r="E24" t="n">
         <v>-15.296</v>
@@ -2326,16 +2326,16 @@
         <v>12.7576</v>
       </c>
       <c r="S24" t="n">
-        <v>0.7468000000000007</v>
+        <v>0.7466000000000002</v>
       </c>
       <c r="T24" t="n">
         <v>-2.6711</v>
       </c>
       <c r="U24" t="n">
-        <v>3.418</v>
+        <v>3.417700000000001</v>
       </c>
       <c r="V24" t="n">
-        <v>1.719</v>
+        <v>1.718999999999999</v>
       </c>
       <c r="W24" t="n">
         <v>3.2477</v>
